--- a/customer-esg-agent/data/factsheet_template.xlsx
+++ b/customer-esg-agent/data/factsheet_template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,11 @@
     </font>
     <font>
       <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -68,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -76,7 +81,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,9 +453,9 @@
   <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -512,204 +520,206 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>지표 고유코드
-(예: E-GHG-S1)</t>
+          <t>(선택)
+비우면 AUTO-001
+자동 부여</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>E/S/G
-대분류</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>지표명</t>
+          <t>(선택)
+E/S/G</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>★필수
+지표명</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>기준연도</t>
+          <t>(권장)
+기준연도</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>사이트
-(이천/청주/전사)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>값</t>
+          <t>(선택)
+이천/청주/전사</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>★필수
+값</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>단위</t>
+          <t>(권장)
+단위</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>출처
-(보고서명·페이지)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>공개가능여부
+          <t>(권장)
+출처(보고서·페이지)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>★필수
 Y=공개가능
-N=대외비(자동 제외)</t>
+N·빈칸=제외</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>(선택)
+비고</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>E-GHG-S1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Scope 1 배출량 (예시)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>전사</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>1234567</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>tCO2eq</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>2026 지속가능경영보고서 p.42</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>예시 행 — 실데이터 입력 후 삭제</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>S-LAB-RBA</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RBA 인증 현황 (예시)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>RBA 인증 현황 (예시·코드 생략)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>전사</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Full Member</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>RBA 회원 등록증</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — 실데이터 입력 후 삭제</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>코드를 비우면 자동 부여됨</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>G-ETH-EDU</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>윤리교육 이수율 (예시)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>전사</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>99.2</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>2026 지속가능경영보고서 p.78</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>예시 행 — N이면 LLM에 전달 안 됨</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>N이면 LLM에 전달 안 됨</t>
         </is>
       </c>
     </row>

--- a/customer-esg-agent/data/factsheet_template.xlsx
+++ b/customer-esg-agent/data/factsheet_template.xlsx
@@ -450,19 +450,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,8 +517,13 @@
           <t>note</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>platform_id</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="54" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>(선택)
@@ -580,6 +586,13 @@
 비고</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>(선택)
+사내플랫폼 지표고유번호
+연결 시 월별·최신값 자동인용</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -626,6 +639,11 @@
       <c r="J3" s="4" t="inlineStr">
         <is>
           <t>예시 행 — 실데이터 입력 후 삭제</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>SKHALGETC001001001001</t>
         </is>
       </c>
     </row>
@@ -671,9 +689,10 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>코드를 비우면 자동 부여됨</t>
-        </is>
-      </c>
+          <t>코드 비우면 자동 부여</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -722,13 +741,14 @@
           <t>N이면 LLM에 전달 안 됨</t>
         </is>
       </c>
+      <c r="K5" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="E, S, G 중 하나를 선택하세요" type="list">
+    <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"E,S,G"</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Y 또는 N만 입력 가능합니다" type="list">
+    <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
